--- a/workbook/rcmi_content_backup_before_ppp_sync.xlsx
+++ b/workbook/rcmi_content_backup_before_ppp_sync.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="28800" windowHeight="17240" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="28800" windowHeight="17240" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="START_HERE" sheetId="1" state="visible" r:id="rId1"/>
@@ -467,7 +467,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="120" customWidth="1" min="2" max="2"/>
@@ -485,7 +485,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>Purpose</t>
@@ -497,7 +497,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>Tab: START_HERE</t>
@@ -509,7 +509,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="16" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>Tab: faculty</t>
@@ -521,7 +521,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="16" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
           <t>Tab: research</t>
@@ -533,7 +533,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="16" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>Tab: publications</t>
@@ -545,7 +545,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="16" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
           <t>Tab: LOOKUPS</t>
@@ -557,7 +557,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="16" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
           <t>Edit These Fields</t>
@@ -581,7 +581,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="16" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
           <t>Do Not Delete Rows</t>
@@ -593,7 +593,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="16" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>Visibility</t>
@@ -605,7 +605,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="16" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
           <t>Dropdowns</t>
@@ -617,7 +617,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="16" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
           <t>Project Links</t>
@@ -629,7 +629,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="16" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>Sorting</t>
@@ -641,7 +641,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="16" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
           <t>Help</t>
@@ -665,7 +665,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AD39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="3"/>
@@ -859,7 +859,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>RCMI IDC leadership</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -922,13 +922,13 @@
           <t>Grant Writing</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="n"/>
       <c r="Z2" t="inlineStr">
         <is>
           <t>./img/faculty/faculty_christine_hohmann.jpg</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>RCMI IDC leadership</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1014,13 +1014,13 @@
           <t>Program Evaluation</t>
         </is>
       </c>
-      <c r="W3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="n"/>
       <c r="Z3" t="inlineStr">
         <is>
           <t>./img/faculty/faculty_shiva_mehravaran.jpg</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="n"/>
       <c r="AC3" t="n">
         <v>2022</v>
       </c>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Principal Investigators</t>
+          <t>RCMI Leadership</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1129,12 +1129,17 @@
           <t>Selected publication metrics and highlights.</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>./img/faculty/faculty_James_Wachira.jpg</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>Dr. James Wachira</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="n"/>
       <c r="AC4" t="n">
         <v>2018</v>
       </c>
@@ -1165,7 +1170,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Principal Investigators</t>
+          <t>RCMI Leadership</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1228,7 +1233,12 @@
           <t>Tobacco Control</t>
         </is>
       </c>
-      <c r="W5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="n"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>./img/faculty/pilot_Payam_Sheikhattari.jpeg</t>
+        </is>
+      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>Dr. Payam Sheikhattari</t>
@@ -1314,7 +1324,7 @@
           <t>Coordination</t>
         </is>
       </c>
-      <c r="W6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="n"/>
       <c r="X6" t="inlineStr">
         <is>
           <t>Portage 113</t>
@@ -1337,8 +1347,13 @@
           <t>pilot_akanksha-anand</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,8 +1385,13 @@
           <t>pilot_lening-olivera-figueroa</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>1</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>101</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,8 +1423,13 @@
           <t>pilot_arif-mahmud</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>102</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1441,8 +1466,13 @@
           <t>pilot_sharde-theodore</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>1</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>103</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1474,8 +1504,13 @@
           <t>pilot_ballington-kinlock</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>1</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>104</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1507,8 +1542,13 @@
           <t>pilot_sharvani-mahadevaraju</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>1</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>105</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1540,8 +1580,13 @@
           <t>pilot_christopher-amissah</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>1</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1556,11 +1601,6 @@
       <c r="J13" t="inlineStr">
         <is>
           <t>christopher.amissah@morgan.edu</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>./img/faculty/pilot_christopher-amissah.jpg</t>
         </is>
       </c>
       <c r="AC13" t="n">
@@ -1578,8 +1618,13 @@
           <t>pilot_tajma-cameron</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>1</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>107</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1611,8 +1656,13 @@
           <t>pilot_dajaneil-mccree</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>1</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>108</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1644,8 +1694,13 @@
           <t>pilot_vishnu-kumar</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>1</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>109</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1677,8 +1732,13 @@
           <t>pilot_kyle-nolla</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>1</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>110</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1693,11 +1753,6 @@
       <c r="J17" t="inlineStr">
         <is>
           <t>kyle.nolla@morgan.edu</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>./img/faculty/pilot_kyle-nolla.jpg</t>
         </is>
       </c>
       <c r="AC17" t="n">
@@ -1715,8 +1770,13 @@
           <t>pilot_samia-kirchner</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>1</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>111</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1753,8 +1813,13 @@
           <t>pilot_chibuike-ibebuchi</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>1</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>112</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1786,8 +1851,13 @@
           <t>pilot_david-fakunle</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>1</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>113</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1819,8 +1889,13 @@
           <t>pilot_leslie-anderson</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>1</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1857,8 +1932,13 @@
           <t>pilot_joshua-burrow</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>1</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>115</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1890,8 +1970,13 @@
           <t>pilot_anna-dellomo</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>1</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1923,8 +2008,13 @@
           <t>pilot_monica-faulkner</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>1</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>117</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1956,8 +2046,13 @@
           <t>pilot_robin-butler</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>1</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1989,8 +2084,13 @@
           <t>pilot_yu-cong</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>1</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>119</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2020,11 +2120,6 @@
       <c r="J26" t="inlineStr">
         <is>
           <t>yu.cong@morgan.edu</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>./img/faculty/pilot_yu-cong.jpg</t>
         </is>
       </c>
       <c r="AC26" t="n">
@@ -2042,8 +2137,13 @@
           <t>pilot_simone-gibson</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>1</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2075,8 +2175,13 @@
           <t>pilot_marciea-mcmillian</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>1</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>121</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2123,8 +2228,13 @@
           <t>pilot_jemal-mohammed-awel</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>1</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>122</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2154,11 +2264,6 @@
       <c r="J29" t="inlineStr">
         <is>
           <t>jemal.mohammed-awel@morgan.edu</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>./img/faculty/pilot_jemal-mohammed-awel.jpg</t>
         </is>
       </c>
       <c r="AC29" t="n">
@@ -2176,8 +2281,13 @@
           <t>pilot_mingchao-cai</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>1</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>123</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2207,11 +2317,6 @@
       <c r="J30" t="inlineStr">
         <is>
           <t>mingchao.cai@morgan.edu</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>./img/faculty/pilot_mingchao-cai.jpg</t>
         </is>
       </c>
       <c r="AC30" t="n">
@@ -2229,8 +2334,13 @@
           <t>pilot_yuejin-li</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>1</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2260,11 +2370,6 @@
       <c r="J31" t="inlineStr">
         <is>
           <t>YueJin.Li@morgan.edu</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>./img/faculty/pilot_yuejin-li.jpg</t>
         </is>
       </c>
       <c r="AC31" t="n">
@@ -2282,8 +2387,13 @@
           <t>pilot_justin-bonny</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>1</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>125</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2313,11 +2423,6 @@
       <c r="J32" t="inlineStr">
         <is>
           <t>justin.bonny@morgan.edu</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>./img/faculty/pilot_justin-bonny.jpg</t>
         </is>
       </c>
       <c r="AC32" t="n">
@@ -2335,8 +2440,13 @@
           <t>pilot_chunlei-fan</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>1</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>126</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2366,11 +2476,6 @@
       <c r="J33" t="inlineStr">
         <is>
           <t>Chunlei.Fan@MORGAN.EDU</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>./img/faculty/pilot_chunlei-fan.jpg</t>
         </is>
       </c>
       <c r="AC33" t="n">
@@ -2388,8 +2493,13 @@
           <t>pilot_shiva-mehravaran</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>1</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>127</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2419,11 +2529,6 @@
       <c r="J34" t="inlineStr">
         <is>
           <t>shiva.mehravaran@morgan.edu</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>./img/faculty/pilot_shiva-mehravaran.jpg</t>
         </is>
       </c>
       <c r="AC34" t="n">
@@ -2441,8 +2546,13 @@
           <t>pilot_thomas-ihde</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>1</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>128</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2489,8 +2599,13 @@
           <t>pilot_ingrid-k-tulloch</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>1</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>129</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2520,11 +2635,6 @@
       <c r="J36" t="inlineStr">
         <is>
           <t>ingrid.tulloch@morgan.edu</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>./img/faculty/pilot_ingrid-k-tulloch.jpg</t>
         </is>
       </c>
       <c r="AC36" t="n">
@@ -2542,8 +2652,13 @@
           <t>pilot_leah-hollis</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>1</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>130</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2590,8 +2705,13 @@
           <t>pilot_robin-spaid</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>1</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>131</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2638,8 +2758,13 @@
           <t>pilot_alexander-samokhvalov</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>1</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>132</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2659,11 +2784,6 @@
       <c r="J39" t="inlineStr">
         <is>
           <t>alexandr.samokhvalov@morgan.edu</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>./img/faculty/pilot_alexander-samokhvalov.jpg</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
@@ -2683,8 +2803,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <dimension ref="A1:AE13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -2857,120 +2977,84 @@
           <t>Internal Notes</t>
         </is>
       </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Featured Research</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>project</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>area_molecular_cellular_biology</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>10</v>
+          <t>ppp_promoting-a-sense-of-risk-to-preventing</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Molecular &amp; Cellular Biology</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Investigating fundamental biological mechanisms at the molecular and cellular level to understand disease processes.</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>🧬</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Cell signaling pathways</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Gene expression regulation</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>RNA-protein interactions</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Melanocortin receptor mechanisms</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="AD2" s="2" t="inlineStr"/>
+          <t>Promoting a Sense of Risk to Preventing Gambling Addiction in Youth</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Promoting a Sense of Risk to Preventing Gambling Addiction in Youth</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Dr. Yu Cong</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Information Science and Systems</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>project</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>area_public_health_disparities</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>20</v>
+          <t>ppp_how-does-a-mismatch-between-childhood-an</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Public Health &amp; Disparities</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Addressing health inequities through community-engaged research and evidence-based interventions.</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>🏥</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Community-based participatory research</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Health disparities intervention</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Tobacco control</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Urban health challenges</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="AD3" s="2" t="inlineStr"/>
+          <t>How does a mismatch between childhood and school SES relate to Black young adults’ excess body weight?</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>How does a mismatch between childhood and school SES relate to Black young adults’ excess body weight?</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Dr. Marciea McMillian</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Teacher Education and Professional Development</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -2980,91 +3064,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>project_melanocortin_signaling</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>30</v>
+          <t>ppp_data-driven-mathematical-assessment-of-t</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Melanocortin Receptor Signaling in Health and Disease</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>faculty_james_wachira</t>
+          <t>Data-driven mathematical assessment of the role of sterile insect technology (SIT) on the population abundance of malaria mosquitoes and disease</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Data-driven mathematical assessment of the role of sterile insect technology (SIT) on the population abundance of malaria mosquitoes and disease</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Dr. James Wachira</t>
+          <t>Dr. Jemal Mohammed-Awel</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>This project delineates the mechanisms of signaling through melanocortin receptors and their implications for obesity, metabolic disorders, and inflammatory diseases.</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Cell Signaling</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Molecular Biology</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Metabolic Disease</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>https://example.org/projects/melanocortin</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>NIH</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>RCMI-001</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2024-01-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Recent review article</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>https://example.org/publications/melanocortin-review</t>
+          <t>Mathematics</t>
         </is>
       </c>
     </row>
@@ -3076,145 +3099,83 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>project_urban_health_interventions</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>40</v>
+          <t>ppp_brain-edema-simulation-by-using-a-multip</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Community-Based Health Interventions in Urban Settings</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>faculty_payam_sheikhattari</t>
+          <t>Brain Edema Simulation by using a Multiple Network Poroelastic Model</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brain Edema Simulation by using a Multiple Network Poroelastic Model</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Dr. Payam Sheikhattari</t>
+          <t>Dr. Mingchao Cai</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Public Health</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>This research employs community-based participatory approaches to address health disparities in urban populations, with a focus on tobacco control and nicotine dependence.</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Public Health</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>CBPR</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Health Disparities</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>https://example.org/projects/urban-health</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>NIH</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>RCMI-002</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Community intervention article</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>https://example.org/publications/urban-interventions</t>
-        </is>
+          <t>Mathematical Modeling</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>infrastructure</t>
+          <t>project</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>infra_biostatistics_unit</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>50</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>📈</t>
+          <t>ppp_the-effect-of-weathered-micro-and-nanopl</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>The effect of Weathered Micro and Nanoplastics on Heart: Implication of Environmental Pollution Inequity and Health Disparity</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>The effect of Weathered Micro and Nanoplastics on Heart: Implication of Environmental Pollution Inequity and Health Disparity</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Dr. YueJin Li</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Statistical consultation and support for study design, data analysis, and manuscript preparation.</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Biostatistics Unit</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr"/>
+          <t>Biology / Medical Technology</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>project</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ppp_promoting-a-sense-of-risk-to-preventing</t>
+          <t>ppp_child-fire-casualty-disparities-develop</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -3222,34 +3183,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Promoting a Sense of Risk to Preventing Gambling Addiction in Youth</t>
+          <t>Child Fire Casualty Disparities: Development of Fire Cue Perception</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Promoting a Sense of Risk to Preventing Gambling Addiction in Youth</t>
+          <t>Child Fire Casualty Disparities: Development of Fire Cue Perception</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Dr. Yu Cong</t>
+          <t>Dr. Justin Bonny</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Information Science and Systems</t>
+          <t>Psychology</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>project</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ppp_how-does-a-mismatch-between-childhood-an</t>
+          <t>ppp_microplastic-in-eastern-oyster-implicat</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -3257,34 +3218,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>How does a mismatch between childhood and school SES relate to Black young adults’ excess body weight?</t>
+          <t>Microplastic in Eastern Oyster: Implications to Human Exposure and Public Health</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>How does a mismatch between childhood and school SES relate to Black young adults’ excess body weight?</t>
+          <t>Microplastic in Eastern Oyster: Implications to Human Exposure and Public Health</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Dr. Marciea McMillian</t>
+          <t>Dr. Chunlei Fan</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Teacher Education and Professional Development</t>
-        </is>
+          <t>Environmental Health</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>project</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ppp_data-driven-mathematical-assessment-of-t</t>
+          <t>ppp_stability-of-tear-microbiota-in-c57bl-6</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -3292,34 +3256,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data-driven mathematical assessment of the role of sterile insect technology (SIT) on the population abundance of malaria mosquitoes and disease</t>
+          <t>Stability of tear microbiota in C57BL/6 mice: an animal model for microbiome studies</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Data-driven mathematical assessment of the role of sterile insect technology (SIT) on the population abundance of malaria mosquitoes and disease</t>
+          <t>Stability of tear microbiota in C57BL/6 mice: an animal model for microbiome studies</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Dr. Jemal Mohammed-Awel</t>
+          <t>Dr. Shiva Mehravaran</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Mathematics</t>
-        </is>
+          <t>Bioinformatics</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>project</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ppp_brain-edema-simulation-by-using-a-multip</t>
+          <t>ppp_estimating-toxic-pfas-concentrations-in</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3327,34 +3294,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brain Edema Simulation by using a Multiple Network Poroelastic Model</t>
+          <t>Estimating Toxic PFAS Concentrations in Seafood Spatially in the Chesapeake Bay</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brain Edema Simulation by using a Multiple Network Poroelastic Model</t>
+          <t>Estimating Toxic PFAS Concentrations in Seafood Spatially in the Chesapeake Bay</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Dr. Mingchao Cai</t>
+          <t>Dr. Thomas Ihde</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Mathematical Modeling</t>
+          <t>Environmental Health</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>project</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ppp_the-effect-of-weathered-micro-and-nanopl</t>
+          <t>ppp_assessing-causal-effects-of-racial-discr</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3362,34 +3329,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The effect of Weathered Micro and Nanoplastics on Heart: Implication of Environmental Pollution Inequity and Health Disparity</t>
+          <t>Assessing Causal Effects of Racial Discrimination on Inflammation</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>The effect of Weathered Micro and Nanoplastics on Heart: Implication of Environmental Pollution Inequity and Health Disparity</t>
+          <t>Assessing Causal Effects of Racial Discrimination on Inflammation</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Dr. YueJin Li</t>
+          <t>Dr. Ingrid K. Tulloch</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Biology / Medical Technology</t>
-        </is>
+          <t>Psychology</t>
+        </is>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>project</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ppp_child-fire-casualty-disparities-develop</t>
+          <t>ppp_workplace-bullying-stress-and-increase</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3397,34 +3367,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Child Fire Casualty Disparities: Development of Fire Cue Perception</t>
+          <t>Workplace Bullying, stress, and increased substance use for URM women medical school faculty</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Child Fire Casualty Disparities: Development of Fire Cue Perception</t>
+          <t>Workplace Bullying, stress, and increased substance use for URM women medical school faculty</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Dr. Justin Bonny</t>
+          <t>Dr. Leah Hollis</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Behavioral Health</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>project</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ppp_microplastic-in-eastern-oyster-implicat</t>
+          <t>ppp_the-role-of-nutrition-and-food-insecurit</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3432,195 +3402,20 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Microplastic in Eastern Oyster: Implications to Human Exposure and Public Health</t>
+          <t>The Role of Nutrition and Food Insecurity in Community College Student Success for African American/Black women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Microplastic in Eastern Oyster: Implications to Human Exposure and Public Health</t>
+          <t>The Role of Nutrition and Food Insecurity in Community College Student Success for African American/Black women</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Dr. Chunlei Fan</t>
+          <t>Dr. Robin Spaid</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
-        <is>
-          <t>Environmental Health</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ppp_stability-of-tear-microbiota-in-c57bl-6</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Stability of tear microbiota in C57BL/6 mice: an animal model for microbiome studies</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Stability of tear microbiota in C57BL/6 mice: an animal model for microbiome studies</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Dr. Shiva Mehravaran</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Bioinformatics</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ppp_estimating-toxic-pfas-concentrations-in</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Estimating Toxic PFAS Concentrations in Seafood Spatially in the Chesapeake Bay</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Estimating Toxic PFAS Concentrations in Seafood Spatially in the Chesapeake Bay</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Dr. Thomas Ihde</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Environmental Health</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ppp_assessing-causal-effects-of-racial-discr</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Assessing Causal Effects of Racial Discrimination on Inflammation</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Assessing Causal Effects of Racial Discrimination on Inflammation</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Dr. Ingrid K. Tulloch</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Psychology</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ppp_workplace-bullying-stress-and-increase</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Workplace Bullying, stress, and increased substance use for URM women medical school faculty</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Workplace Bullying, stress, and increased substance use for URM women medical school faculty</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Dr. Leah Hollis</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Behavioral Health</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ppp_the-role-of-nutrition-and-food-insecurit</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>The Role of Nutrition and Food Insecurity in Community College Student Success for African American/Black women</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>The Role of Nutrition and Food Insecurity in Community College Student Success for African American/Black women</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Dr. Robin Spaid</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
         <is>
           <t>Health Policy &amp; Education</t>
         </is>
@@ -3638,9 +3433,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="42.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
@@ -3768,7 +3563,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -3832,7 +3627,7 @@
           <t>https://example.org/publications/melanocortin-review</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" t="inlineStr">
@@ -3847,7 +3642,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -3906,7 +3701,7 @@
           <t>https://example.org/publications/rna-pathway-regulation</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -3921,7 +3716,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -3985,7 +3780,7 @@
           <t>https://example.org/publications/urban-interventions</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -4054,7 +3849,7 @@
           <t>https://example.org/publications/urban-report</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4817,8 +4612,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="n">
-        <v>1</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4845,8 +4642,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="C22" t="n">
-        <v>1</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4873,8 +4672,15 @@
       </c>
     </row>
     <row r="23">
-      <c r="C23" t="n">
-        <v>1</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ppp_brain-edema-simulation-by-using-a-multip</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4901,8 +4707,15 @@
       </c>
     </row>
     <row r="24">
-      <c r="C24" t="n">
-        <v>1</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ppp_assessing-causal-effects-of-racial-discr</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4929,8 +4742,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="C25" t="n">
-        <v>1</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4957,8 +4772,15 @@
       </c>
     </row>
     <row r="26">
-      <c r="C26" t="n">
-        <v>1</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ppp_brain-edema-simulation-by-using-a-multip</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4985,8 +4807,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="C27" t="n">
-        <v>1</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -5013,8 +4837,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="C28" t="n">
-        <v>1</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -5041,8 +4867,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="C29" t="n">
-        <v>1</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -5064,8 +4892,15 @@
       </c>
     </row>
     <row r="30">
-      <c r="C30" t="n">
-        <v>1</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ppp_brain-edema-simulation-by-using-a-multip</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -5092,8 +4927,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="C31" t="n">
-        <v>1</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -5120,8 +4957,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="C32" t="n">
-        <v>1</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -5148,8 +4987,15 @@
       </c>
     </row>
     <row r="33">
-      <c r="C33" t="n">
-        <v>1</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ppp_brain-edema-simulation-by-using-a-multip</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -5176,8 +5022,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="C34" t="n">
-        <v>1</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -5204,8 +5052,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="C35" t="n">
-        <v>1</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -5232,8 +5082,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="C36" t="n">
-        <v>1</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -5260,8 +5112,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="C37" t="n">
-        <v>1</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -5288,8 +5142,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="C38" t="n">
-        <v>1</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -5316,8 +5172,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="C39" t="n">
-        <v>1</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -5344,8 +5202,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" t="n">
-        <v>1</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -5372,8 +5232,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="C41" t="n">
-        <v>1</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -5400,8 +5262,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="C42" t="n">
-        <v>1</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -5433,8 +5297,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="C43" t="n">
-        <v>1</v>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -5461,8 +5327,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="C44" t="n">
-        <v>1</v>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -5489,8 +5357,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="C45" t="n">
-        <v>1</v>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -5517,8 +5387,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="C46" t="n">
-        <v>1</v>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -5550,8 +5422,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="C47" t="n">
-        <v>1</v>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -5578,8 +5452,15 @@
       </c>
     </row>
     <row r="48">
-      <c r="C48" t="n">
-        <v>1</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ppp_brain-edema-simulation-by-using-a-multip</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -5611,8 +5492,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="C49" t="n">
-        <v>1</v>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -5639,8 +5522,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="C50" t="n">
-        <v>1</v>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -5667,8 +5552,15 @@
       </c>
     </row>
     <row r="51">
-      <c r="C51" t="n">
-        <v>1</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ppp_stability-of-tear-microbiota-in-c57bl-6</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -5695,8 +5587,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="C52" t="n">
-        <v>1</v>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -5723,8 +5617,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="C53" t="n">
-        <v>1</v>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -5751,8 +5647,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="C54" t="n">
-        <v>1</v>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -5779,8 +5677,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="C55" t="n">
-        <v>1</v>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -5807,8 +5707,15 @@
       </c>
     </row>
     <row r="56">
-      <c r="C56" t="n">
-        <v>1</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ppp_stability-of-tear-microbiota-in-c57bl-6</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -5835,8 +5742,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="C57" t="n">
-        <v>1</v>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -5868,8 +5777,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="C58" t="n">
-        <v>1</v>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -5901,8 +5812,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="C59" t="n">
-        <v>1</v>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -5929,8 +5842,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="C60" t="n">
-        <v>1</v>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -5957,8 +5872,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="C61" t="n">
-        <v>1</v>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -5985,8 +5902,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="C62" t="n">
-        <v>1</v>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -6013,8 +5932,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="C63" t="n">
-        <v>1</v>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -6041,8 +5962,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="C64" t="n">
-        <v>1</v>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -6074,8 +5997,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="C65" t="n">
-        <v>1</v>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -6102,8 +6027,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="C66" t="n">
-        <v>1</v>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -6130,8 +6057,15 @@
       </c>
     </row>
     <row r="67">
-      <c r="C67" t="n">
-        <v>1</v>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ppp_assessing-causal-effects-of-racial-discr</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -6158,8 +6092,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="C68" t="n">
-        <v>1</v>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -6186,8 +6122,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="C69" t="n">
-        <v>1</v>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -6214,8 +6152,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="C70" t="n">
-        <v>1</v>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -6242,8 +6182,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="C71" t="n">
-        <v>1</v>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -6270,8 +6212,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="C72" t="n">
-        <v>1</v>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -6298,8 +6242,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="C73" t="n">
-        <v>1</v>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -6326,8 +6272,15 @@
       </c>
     </row>
     <row r="74">
-      <c r="C74" t="n">
-        <v>1</v>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ppp_how-does-a-mismatch-between-childhood-an</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -6354,8 +6307,15 @@
       </c>
     </row>
     <row r="75">
-      <c r="C75" t="n">
-        <v>1</v>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ppp_assessing-causal-effects-of-racial-discr</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -6382,8 +6342,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="C76" t="n">
-        <v>1</v>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -6410,8 +6372,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="C77" t="n">
-        <v>1</v>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -6438,8 +6402,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="C78" t="n">
-        <v>1</v>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -6471,8 +6437,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="C79" t="n">
-        <v>1</v>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -6499,8 +6467,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="C80" t="n">
-        <v>1</v>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -6527,8 +6497,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="C81" t="n">
-        <v>1</v>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -6555,8 +6527,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="C82" t="n">
-        <v>1</v>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -6583,8 +6557,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="C83" t="n">
-        <v>1</v>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -6611,8 +6587,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="C84" t="n">
-        <v>1</v>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -6639,8 +6617,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="C85" t="n">
-        <v>1</v>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -6667,8 +6647,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="C86" t="n">
-        <v>1</v>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -6695,8 +6677,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="C87" t="n">
-        <v>1</v>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -6723,8 +6707,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="C88" t="n">
-        <v>1</v>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -6746,8 +6732,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="C89" t="n">
-        <v>1</v>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -6774,8 +6762,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="C90" t="n">
-        <v>1</v>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -6802,8 +6792,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="C91" t="n">
-        <v>1</v>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -6830,8 +6822,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="C92" t="n">
-        <v>1</v>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -6858,8 +6852,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="C93" t="n">
-        <v>1</v>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -6886,8 +6882,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="C94" t="n">
-        <v>1</v>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -6914,8 +6912,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="C95" t="n">
-        <v>1</v>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -6942,8 +6942,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="C96" t="n">
-        <v>1</v>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -6970,8 +6972,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="C97" t="n">
-        <v>1</v>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -6998,8 +7002,15 @@
       </c>
     </row>
     <row r="98">
-      <c r="C98" t="n">
-        <v>1</v>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ppp_microplastic-in-eastern-oyster-implicat</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -7026,8 +7037,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="C99" t="n">
-        <v>1</v>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -7054,8 +7067,15 @@
       </c>
     </row>
     <row r="100">
-      <c r="C100" t="n">
-        <v>1</v>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ppp_the-effect-of-weathered-micro-and-nanopl</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -7082,8 +7102,15 @@
       </c>
     </row>
     <row r="101">
-      <c r="C101" t="n">
-        <v>1</v>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ppp_brain-edema-simulation-by-using-a-multip</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -7121,7 +7148,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
